--- a/retrieval-foundry/rag-engine/evaluation/deepeval/RAG_Evaluation_Results.xlsx
+++ b/retrieval-foundry/rag-engine/evaluation/deepeval/RAG_Evaluation_Results.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VECTORDBCREATION\rag_evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FB3FA2-CF0D-4E23-A5D6-94D3B10532D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B35440D-ABA0-4703-87CB-6AA1BF47A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Question</t>
   </si>
@@ -49,77 +49,76 @@
     <t>What are the eligibility and concentration limits for second-lien, unsecured, and CCC assets?</t>
   </si>
   <si>
-    <t>What are the reinvestment periods?</t>
-  </si>
-  <si>
-    <t>What are the target collateral balances?</t>
-  </si>
-  <si>
-    <t>Compare the diversity scores of these?</t>
-  </si>
-  <si>
-    <t>What are the single obligor concentration limits?</t>
-  </si>
-  <si>
-    <t>What are the WARF limits or caps of these?</t>
-  </si>
-  <si>
-    <t>What is the capital structure?</t>
-  </si>
-  <si>
-    <t>Eligibility and concentration limits (HarborView CLO 2026‑1)  
+    <t>**Eligibility and concentration limits (HarborView CLO 2026‑1)**  
 | Asset type | Concentration limit |
 |------------|---------------------|
-| Second‑lien assets | Maximum 10.0 % of the collateral balance |
-| Unsecured assets | Maximum 5.0 % of the collateral balance |
-| CCC or lower credit‑rated assets | Maximum 7.5 % of the collateral balance |
-These limits are listed in Table 5 of the document, which summarizes the eligibility and concentration standards for the CLO.</t>
-  </si>
-  <si>
-    <t>Reinvestment periods by document
-| Document | Reinvestment period (end date) | Source |
-|----------|--------------------------------|--------|
-| Oakmont CLO 2026‑1 | May 20, 2029 | Oakmont_CLO_2026-1.pdf – Section 13.3 |
-| BlueRiver CLO 2026‑2 | January 20, 2030 | BlueRiver_CLO_2026-2.pdf – Section 12.1 |
-| Redwood CLO 2026‑1 | June 20, 2029 | Redwood_CLO_2026-1.pdf – Section 18.1 (and Section 10.2) |
-These dates mark the termination of each document’s active reinvestment period.</t>
-  </si>
-  <si>
-    <t>Target collateral balances
-| Document | Target collateral balance |
-|----------|---------------------------|
-| 01_Northstar_CLO_2026‑1_professional.pdf | $465,000,000 (initial target collateral balance)【01_Northstar_CLO_2026-1_professional.pdf】 |
-| Crescent_CLO_2026‑2.pdf | $500,000,000 (target collateral)【Crescent_CLO_2026-2.pdf】 |
-*No target collateral information was extracted from Silverbrook_CLO_2026‑1.pdf.*</t>
-  </si>
-  <si>
-    <t>Diversity Scores
-| Document | Diversity Score |
+| Second‑lien assets | **Maximum 10.0 %** of the collateral balance |
+| Unsecured assets | **Maximum 5.0 %** of the collateral balance |
+| CCC or lower credit‑rated assets | **Maximum 7.5 %** of the collateral balance (higher exposure triggers test consequences) |
+These limits are listed in Table 5 of the document, which summarizes the specific eligibility and concentration standards for the CLO.</t>
+  </si>
+  <si>
+    <t>What are the reinvestment period end dates?</t>
+  </si>
+  <si>
+    <t>**Reinvestment periods (as stated in the documents):**
+| Document | Reinvestment period end date | Source |
+|----------|-----------------------------|--------|
+| Oakmont_CLO_2026‑1.pdf | May 20, 2029 | Section 13.3, page 4 |
+| BlueRiver_CLO_2026‑2.pdf | January 20, 2030 | Section 12.1, page 4 |
+| Redwood_CLO_2026‑1.pdf | June 20, 2029 | Section 18 (Defined Terms), page 5; Section 10, page 3 |
+These dates represent the termination of the active reinvestment period for each CLO.</t>
+  </si>
+  <si>
+    <t>What are the target collateral balances?</t>
+  </si>
+  <si>
+    <t>Compare the diversity scores of these?</t>
+  </si>
+  <si>
+    <t>**Diversity scores**
+| Document | Diversity score |
 |----------|-----------------|
-| BlueRiver_CLO_2026-2.pdf | 66.4 |
-| HarborView_CLO_2026-1.pdf | 58.2 |
-Comparison
-- BlueRiver’s portfolio has a higher diversity score (66.4) than HarborView’s portfolio (58.2).</t>
-  </si>
-  <si>
-    <t>Single obligor concentration limits
+| BlueRiver CLO 2026‑2 | 66.4【BlueRiver_CLO_2026-2.pdf】 |
+| HarborView CLO 2026‑1 | 58.2【HarborView_CLO_2026-1.pdf】 |
+**Comparison**
+BlueRiver CLO 2026‑2 has a higher diversity score (66.4) than HarborView CLO 2026‑1 (58.2).</t>
+  </si>
+  <si>
+    <t>What are the single obligor concentration limits?</t>
+  </si>
+  <si>
+    <t>**Single obligor concentration limits**
 | Document | Limit |
 |----------|-------|
 | BlueRiver_CLO_2026‑2.pdf | 2.25 % of the portfolio【BlueRiver_CLO_2026-2.pdf】 |
-| Oakmont_CLO_2026‑1.pdf | 2.00 % of the portfolio【Oakmont_CLO_2026-1.pdf】 |
-| Redwood_CLO_2026‑1.pdf | 2.00 % of the portfolio【Redwood_CLO_2026-1.pdf】 |
-These are the limits specified in each respective document.</t>
-  </si>
-  <si>
-    <t>WARF limits (caps) by document
-| Document | WARF cap | Source |
-|----------|----------|--------|
-| Crescent_CLO_2026-2.pdf | 3,100 | Page 2, Section 2. Collateral Portfolio and Quality |
-| Meridian_CLO_2026-1.pdf | 3,000 | Page 2, Section 2. Collateral Portfolio and Concentration Framework |
-| Pinecrest_CLO_2026-2.pdf | 2,900 | Page 3, Section 3.3 Collateral Quality Tests |</t>
-  </si>
-  <si>
-    <t>Capital structure (as described in Section 2 of the document)  
+| Oakmont_CLO_2026‑1.pdf | 2.00 %【Oakmont_CLO_2026-1.pdf】 |
+| Redwood_CLO_2026‑1.pdf | 2.00 %【Redwood_CLO_2026-1.pdf】 |
+These are the limits stated in each respective document.</t>
+  </si>
+  <si>
+    <t>What are the WARF limits or caps of these?</t>
+  </si>
+  <si>
+    <t>What is the capital structure?</t>
+  </si>
+  <si>
+    <t>The initial collateral balance is **$465,000,000**.</t>
+  </si>
+  <si>
+    <t>**Class A Over‑Collateralization (OC)**  
+- Required threshold: **128.5 %**  
+- Opening cushion: **+6.2 %** (opening value 134.7 % vs. required 128.5 %)
+**Class A In‑Collateral (IC)**  
+- Required threshold: **118.0 %**  
+- Opening cushion: **+23.2 %** (opening value 141.2 % vs. required 118.0 %)</t>
+  </si>
+  <si>
+    <t>The collateral manager is **Apex Meridian Asset Management**.</t>
+  </si>
+  <si>
+    <t>**Capital structure (Section 2 – Capital Structure)**  
+The issuance is organized into seven layers: six rated classes (A‑1 through E) and one subordinated, non‑rated class.  
 | Class | Principal amount | Rating | Coupon / spread | Priority | Approx. subordination |
 |-------|------------------|--------|-----------------|----------|-----------------------|
 | Class A‑1 Notes | $312 million | AAA | SOFR + 1.72 % | First | 40.0 % |
@@ -129,27 +128,46 @@
 | Class D Notes | $26 million | BB | SOFR + 5.10 % | Fifth | 14.0 % |
 | Class E Notes | $20.8 million | B‑ | SOFR + 7.25 % | Sixth | 10.0 % |
 | Subordinated Notes | $52 million | NR | Residual | Last | Residual |
-Key points
-* The structure comprises five rated classes (A‑1 through E) plus a subordinated interest.  
-* Total rated principal: $468.0 million.  
-* Subordinated principal: $52.0 million (NR).  
-* Overall capitalization: $520.0 million, with subordinated notes representing 10.0 % of the initial capitalization.  
-* Seniority follows the order listed above, with the subordinated notes being the last priority.  
-These details are taken from the table and summary in Section 2 of the document.</t>
-  </si>
-  <si>
-    <t>The initial collateral balance is $465,000,000.</t>
-  </si>
-  <si>
-    <t>Class A Over‑Collateralization (OC)  
-- Required threshold: 128.5 %  
-- Opening cushion: +6.2 % (opening value 134.7 % vs. required 128.5 %)
-Class A In‑Collateral (IC)  
-- Required threshold: 118.0 %  
-- Opening cushion: +23.2 % (opening value 141.2 % vs. required 118.0 %)</t>
-  </si>
-  <si>
-    <t>The collateral manager is Apex Meridian Asset Management.</t>
+- **Total rated principal**: $468.0 million.  
+- **Subordinated principal**: $52.0 million (10.0 % of the initial capitalization).  
+- **Overall capitalization**: $520.0 million.  
+The structure follows a senior‑to‑junior hierarchy, with coupon spreads increasing as ratings decline and subordination percentages decreasing with seniority.</t>
+  </si>
+  <si>
+    <t>**Target collateral balances**\n\n| Document | Target collateral balance |\n|----------|---------------------------|\n| 01_Northstar_CLO_2026‑1_professional.pdf | $465,000,000 (initial target collateral balance)【01_Northstar_CLO_2026-1_professional.pdf】 |\n| Crescent_CLO_2026‑2.pdf | $500,000,000 (target collateral)【Crescent_CLO_2026-2.pdf】 |\n\n*No target collateral information was extracted from Silverbrook_CLO_2026‑1.pdf.</t>
+  </si>
+  <si>
+    <t>Selected Files</t>
+  </si>
+  <si>
+    <t>01_Northstar_CLO_2026-1_professional.pdf</t>
+  </si>
+  <si>
+    <t>BlueRiver_CLO_2026-2.pdf</t>
+  </si>
+  <si>
+    <t>HarborView_CLO_2026-1.pdf</t>
+  </si>
+  <si>
+    <t>Oakmont_CLO_2026-1.pdf, BlueRiver_CLO_2026-2.pdf, Redwood_CLO_2026-1.pdf</t>
+  </si>
+  <si>
+    <t>01_Northstar_CLO_2026-1_professional.pdf, Silverbrook_CLO_2026-1.pdf, Crescent_CLO_2026-2.pdf</t>
+  </si>
+  <si>
+    <t>BlueRiver_CLO_2026-2.pdf, HarborView_CLO_2026-1.pdf</t>
+  </si>
+  <si>
+    <t>BlueRiver_CLO_2026-2.pdf, Oakmont_CLO_2026-1.pdf, Redwood_CLO_2026-1.pdf</t>
+  </si>
+  <si>
+    <t>Crescent_CLO_2026-2.pdf, Meridian_CLO_2026-1.pdf, Pinecrest_CLO_2026-2.pdf</t>
+  </si>
+  <si>
+    <t>Summit_CLO_2026_2_document.pdf</t>
+  </si>
+  <si>
+    <t>**WARF limits (caps) by document**\n\n| Document | WARF cap | Source |\n|----------|----------|--------|\n| Crescent_CLO_2026-2.pdf | 3,100 | Page 2, Section 2. Collateral Portfolio and Quality |\n| Meridian_CLO_2026-1.pdf | 3,000 | Page 2, Section 2. Collateral Portfolio and Concentration Framework |\n| Pinecrest_CLO_2026-2.pdf | 2,900 | Page 3, Section 3.3 Collateral Quality Tests |</t>
   </si>
 </sst>
 </file>
@@ -520,35 +538,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -556,157 +577,187 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>0.95</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.95</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>0.95</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.95</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="C8">
-        <v>0.85</v>
-      </c>
-      <c r="D8">
-        <v>0.9</v>
-      </c>
-      <c r="E8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
       <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <v>1</v>
       </c>
     </row>
